--- a/KatalonData/EmailTextToPay/Manage_EmailText_Upgrade.xlsx
+++ b/KatalonData/EmailTextToPay/Manage_EmailText_Upgrade.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="147">
   <si>
     <t>Result</t>
   </si>
@@ -467,6 +467,117 @@
   </si>
   <si>
     <t>Tue Jul 14 17:54:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:39:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:41:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:42:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:43:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:44:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:45:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:45:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:46:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:47:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:47:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:48:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:48:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:49:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:49:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:50:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:51:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:51:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:52:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:52:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:53:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:53:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:54:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:55:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:56:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:57:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:58:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:59:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:59:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:00:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:01:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:02:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:03:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:04:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:05:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:06:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:07:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 09:07:14 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1119,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>54</v>
@@ -1025,7 +1136,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>54</v>
@@ -1091,7 +1202,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>14</v>
@@ -1147,7 +1258,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
@@ -1203,7 +1314,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
@@ -1259,7 +1370,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>15</v>
@@ -1322,7 +1433,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>32</v>
@@ -1343,7 +1454,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>33</v>
@@ -1370,7 +1481,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>28</v>
@@ -1393,7 +1504,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>29</v>
@@ -1416,7 +1527,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>30</v>
@@ -1439,7 +1550,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>31</v>
@@ -1462,7 +1573,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>43</v>
@@ -1485,7 +1596,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>97</v>
+        <v>131</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>44</v>
@@ -1508,7 +1619,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>45</v>
@@ -1574,7 +1685,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="C2" s="18" t="s">
         <v>36</v>
@@ -1600,7 +1711,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C4" s="18" t="s">
         <v>39</v>
@@ -1620,7 +1731,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>40</v>
@@ -1640,7 +1751,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>41</v>
@@ -1663,7 +1774,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>21</v>
@@ -1686,7 +1797,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>22</v>
@@ -1709,7 +1820,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>23</v>
@@ -1736,7 +1847,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>38</v>
@@ -1814,7 +1925,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>48</v>
@@ -1891,7 +2002,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>49</v>
@@ -1968,7 +2079,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>50</v>
@@ -2045,7 +2156,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>10</v>
@@ -2122,7 +2233,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>11</v>
@@ -2199,7 +2310,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>12</v>
@@ -2256,7 +2367,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>81</v>
+        <v>143</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>13</v>
@@ -2325,7 +2436,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>51</v>
@@ -2394,7 +2505,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>52</v>
@@ -2459,7 +2570,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>84</v>
+        <v>133</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>14</v>
@@ -2515,7 +2626,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>14</v>
